--- a/artfynd/S 4298-2024 artfynd.xlsx
+++ b/artfynd/S 4298-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6757766</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6762126</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336847</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336848</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1476,6 +1511,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336940</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117185674</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117753341</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321550</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1933,6 +1988,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321556</t>
         </is>
       </c>
     </row>
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336941</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2173,6 +2238,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127641424</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2294,6 +2364,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321552</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2414,6 +2489,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336864</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2544,6 +2624,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321547</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2674,6 +2759,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321549</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2804,6 +2894,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321553</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2913,6 +3008,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79336959</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3023,6 +3123,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110604439</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3128,6 +3233,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127641725</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3242,6 +3352,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127641374</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3356,8 +3471,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128190862</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>